--- a/Notes/Class/Kodewala_Batch_Zoom_Recordings_and_Tests.xlsx
+++ b/Notes/Class/Kodewala_Batch_Zoom_Recordings_and_Tests.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Java-Backend-Development-Journey-\Notes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Java-Backend-Development-Journey-\Notes\Class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF495735-9667-4677-AAF0-B712A6B85949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7212A5-2550-44FB-8D2D-02CED85338C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="145">
   <si>
     <t>Kodewala Academy - 25th Aug Batch 2026</t>
   </si>
@@ -416,9 +416,6 @@
     <t>https://testmoz.com/15641918</t>
   </si>
   <si>
-    <t>560045</t>
-  </si>
-  <si>
     <t>Test 2</t>
   </si>
   <si>
@@ -428,9 +425,6 @@
     <t>https://testmoz.com/15658424</t>
   </si>
   <si>
-    <t>560011</t>
-  </si>
-  <si>
     <t>Test 3</t>
   </si>
   <si>
@@ -440,9 +434,6 @@
     <t>https://testmoz.com/15679746</t>
   </si>
   <si>
-    <t>560025</t>
-  </si>
-  <si>
     <t>Test 4</t>
   </si>
   <si>
@@ -462,13 +453,16 @@
   </si>
   <si>
     <t>^ys5N^7a</t>
+  </si>
+  <si>
+    <t>Oop's - Encapsulation Session</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,14 +499,42 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF8A1F11"/>
       <name val="Consolas"/>
+      <family val="3"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -571,9 +593,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -589,9 +611,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -601,13 +620,37 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -913,14 +956,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="75" customWidth="1"/>
+    <col min="4" max="4" width="87.1796875" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
@@ -933,548 +978,552 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="C6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="18" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="C9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="C11" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="16" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="6" t="s">
+      <c r="C13" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="16" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="C14" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="C15" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="16" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="C17" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="16" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="C18" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="C19" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="16" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="C20" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="C21" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="16" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="C22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="18" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="6" t="s">
+      <c r="C23" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="16" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="18" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="6" t="s">
+      <c r="C25" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="16" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="18" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="C27" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="16" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="10" t="s">
+      <c r="C28" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="18" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="C29" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="16" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="C30" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="18" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="6" t="s">
+      <c r="C31" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="16" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="C32" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="18" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="20">
+        <v>46310</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="B33" s="13">
-        <v>46310</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>146</v>
-      </c>
-    </row>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D32" r:id="rId1" xr:uid="{9AFE0CE7-2493-40F9-B5D4-B81F15459F22}"/>
     <hyperlink ref="D33" r:id="rId2" xr:uid="{40038E6B-5021-4E43-8794-D01495599744}"/>
+    <hyperlink ref="D30" r:id="rId3" xr:uid="{4B33830F-8820-46FB-A14D-8A613E07AF9D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>125</v>
       </c>
@@ -1487,11 +1536,8 @@
       <c r="D4" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>128</v>
       </c>
@@ -1504,58 +1550,46 @@
       <c r="D5" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="B6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="10" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="B8" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="D8" s="9" t="s">
         <v>139</v>
       </c>
     </row>

--- a/Notes/Class/Kodewala_Batch_Zoom_Recordings_and_Tests.xlsx
+++ b/Notes/Class/Kodewala_Batch_Zoom_Recordings_and_Tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Java-Backend-Development-Journey-\Notes\Class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7212A5-2550-44FB-8D2D-02CED85338C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FF2610-4B63-4247-8168-56259B3C96E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="149">
   <si>
     <t>Kodewala Academy - 25th Aug Batch 2026</t>
   </si>
@@ -456,6 +456,18 @@
   </si>
   <si>
     <t>Oop's - Encapsulation Session</t>
+  </si>
+  <si>
+    <t>Day 30</t>
+  </si>
+  <si>
+    <t>oop's Inheritance &amp; Types</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/rec/share/-nHm7uw0y8nPZrAokjYRiVwsgZfMpvhyWYal2lIR_KSCSqQ_Czu_zDSS9ovgM4QI.Z_Y-0MP9T11pAvtx</t>
+  </si>
+  <si>
+    <t>gVw?36s^</t>
   </si>
 </sst>
 </file>
@@ -595,7 +607,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -652,6 +664,9 @@
     </xf>
     <xf numFmtId="14" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -956,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1489,16 +1504,33 @@
         <v>143</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="20">
+        <v>46311</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>148</v>
+      </c>
+    </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D32" r:id="rId1" xr:uid="{9AFE0CE7-2493-40F9-B5D4-B81F15459F22}"/>
     <hyperlink ref="D33" r:id="rId2" xr:uid="{40038E6B-5021-4E43-8794-D01495599744}"/>
     <hyperlink ref="D30" r:id="rId3" xr:uid="{4B33830F-8820-46FB-A14D-8A613E07AF9D}"/>
+    <hyperlink ref="D34" r:id="rId4" xr:uid="{388D64DF-7DAC-4F7C-BEDB-BF43D76769C0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 

--- a/Notes/Class/Kodewala_Batch_Zoom_Recordings_and_Tests.xlsx
+++ b/Notes/Class/Kodewala_Batch_Zoom_Recordings_and_Tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Java-Backend-Development-Journey-\Notes\Class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FF2610-4B63-4247-8168-56259B3C96E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3DFC43-77EB-4817-A882-DBDAFE36A421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="153">
   <si>
     <t>Kodewala Academy - 25th Aug Batch 2026</t>
   </si>
@@ -468,6 +468,18 @@
   </si>
   <si>
     <t>gVw?36s^</t>
+  </si>
+  <si>
+    <t>Day 31</t>
+  </si>
+  <si>
+    <t>oop's Abstraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://us06web.zoom.us/rec/share/N6GmcN_6v4DhV_GcDM0IuyPuGlJsn-nQ8nDkSxGI5-IACZ9CNhZGIXwvT8YQ7vIr.oQPV1m8CYm20KXuK </t>
+  </si>
+  <si>
+    <t>gzqr=#x7</t>
   </si>
 </sst>
 </file>
@@ -971,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1521,16 +1533,34 @@
         <v>148</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" s="20">
+        <v>46314</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D32" r:id="rId1" xr:uid="{9AFE0CE7-2493-40F9-B5D4-B81F15459F22}"/>
     <hyperlink ref="D33" r:id="rId2" xr:uid="{40038E6B-5021-4E43-8794-D01495599744}"/>
     <hyperlink ref="D30" r:id="rId3" xr:uid="{4B33830F-8820-46FB-A14D-8A613E07AF9D}"/>
     <hyperlink ref="D34" r:id="rId4" xr:uid="{388D64DF-7DAC-4F7C-BEDB-BF43D76769C0}"/>
+    <hyperlink ref="D35" r:id="rId5" xr:uid="{F9F766B3-B1B2-4252-B68F-AF35E8347C31}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 

--- a/Notes/Class/Kodewala_Batch_Zoom_Recordings_and_Tests.xlsx
+++ b/Notes/Class/Kodewala_Batch_Zoom_Recordings_and_Tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Java-Backend-Development-Journey-\Notes\Class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3DFC43-77EB-4817-A882-DBDAFE36A421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37625C3-F53D-47E9-ADE6-60364122DB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="179">
   <si>
     <t>Kodewala Academy - 25th Aug Batch 2026</t>
   </si>
@@ -65,9 +65,6 @@
     <t>27/08/2026</t>
   </si>
   <si>
-    <t>Core Java Session</t>
-  </si>
-  <si>
     <t>https://us06web.zoom.us/rec/share/sQ6aq9h0CyJwebGS9jXjDiROjSA2xfDrEzFjWd5TvYDuWt7ACJgy3g3ZY030fppc.berkYgbCQHWDDB6A</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
     <t>10/09/2026</t>
   </si>
   <si>
-    <t>Class Resumed Session</t>
-  </si>
-  <si>
     <t>https://us06web.zoom.us/rec/share/b5UPDCNKKVEptO1hjEteeRv5rxnKWwcINZpPxT8Y9CWdRQiWaCDgCo18OVOYM1BJ.KwnDWG4rh7wG5ItE</t>
   </si>
   <si>
@@ -119,9 +113,6 @@
     <t>12/09/2026</t>
   </si>
   <si>
-    <t>Extra Saturday Session</t>
-  </si>
-  <si>
     <t>https://us06web.zoom.us/rec/share/es_V8mmAcjc0Ie4mp7lWYKZsG6qCi4vMCI6yNJpaN3M032YwAa4ofVLFs8usDM1b.2DC8htgk995YmXpE</t>
   </si>
   <si>
@@ -446,24 +437,15 @@
     <t>Day 29</t>
   </si>
   <si>
-    <t>oop's Inheritance Session</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://us06web.zoom.us/rec/share/xPXSJdO5ArJba0hT_4Oe073xpBy-JzKNmT1DJXuH1001n1JTd_sfY20DE00Al1Am.d9IoOG85I3Ntn2Ki </t>
   </si>
   <si>
     <t>^ys5N^7a</t>
   </si>
   <si>
-    <t>Oop's - Encapsulation Session</t>
-  </si>
-  <si>
     <t>Day 30</t>
   </si>
   <si>
-    <t>oop's Inheritance &amp; Types</t>
-  </si>
-  <si>
     <t>https://us06web.zoom.us/rec/share/-nHm7uw0y8nPZrAokjYRiVwsgZfMpvhyWYal2lIR_KSCSqQ_Czu_zDSS9ovgM4QI.Z_Y-0MP9T11pAvtx</t>
   </si>
   <si>
@@ -473,20 +455,116 @@
     <t>Day 31</t>
   </si>
   <si>
-    <t>oop's Abstraction</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://us06web.zoom.us/rec/share/N6GmcN_6v4DhV_GcDM0IuyPuGlJsn-nQ8nDkSxGI5-IACZ9CNhZGIXwvT8YQ7vIr.oQPV1m8CYm20KXuK </t>
   </si>
   <si>
     <t>gzqr=#x7</t>
+  </si>
+  <si>
+    <t>𝗨𝗻𝗱𝗲𝗿𝘀𝘁𝗮𝗻𝗱𝗶𝗻𝗴 𝗔𝗯𝘀𝘁𝗿𝗮𝗰𝘁𝗶𝗼𝗻</t>
+  </si>
+  <si>
+    <t>Deep Dive into Inheritance</t>
+  </si>
+  <si>
+    <t>Understanding Inheritance</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Encapsulation Session</t>
+  </si>
+  <si>
+    <t>Static &amp; Instance Initialization Blocks</t>
+  </si>
+  <si>
+    <t>Final keyword</t>
+  </si>
+  <si>
+    <t>basic String concepts</t>
+  </si>
+  <si>
+    <t>String Objects and String Concatenation</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>Switch Statement</t>
+  </si>
+  <si>
+    <t>Git &amp; GitHub</t>
+  </si>
+  <si>
+    <t>taking user inpu</t>
+  </si>
+  <si>
+    <t>Arrays and for loops</t>
+  </si>
+  <si>
+    <t>Control Flow — if, else if, and else</t>
+  </si>
+  <si>
+    <t>this() and super() applying them to real-world style</t>
+  </si>
+  <si>
+    <t>this() vs super()</t>
+  </si>
+  <si>
+    <t>Real World Problem constructor</t>
+  </si>
+  <si>
+    <t>basics of constructors</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> learning Constructors</t>
+  </si>
+  <si>
+    <t>From Notepad → Eclipse IDE</t>
+  </si>
+  <si>
+    <t>Access Modifiers</t>
+  </si>
+  <si>
+    <t>Methods in Java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operators </t>
+  </si>
+  <si>
+    <t>data types</t>
+  </si>
+  <si>
+    <t>Java Data Types</t>
+  </si>
+  <si>
+    <t>deeper into JDK, JRE and JVM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Command Line Arguments</t>
+  </si>
+  <si>
+    <t>How Java code gets executed</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> writing and running Java programs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://us06web.zoom.us/rec/share/NgwILOCocWHJHQIf4lY8e6amYZtL8gPboDrsn43wsa-LqROD2Ege-tbnd6o6GTCa.hDn9604S3PN7ZQf_ </t>
+  </si>
+  <si>
+    <t>Day 32</t>
+  </si>
+  <si>
+    <t>7B^U9u$h</t>
+  </si>
+  <si>
+    <t>Polymorphism</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,6 +642,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -619,7 +708,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -644,9 +733,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -656,9 +742,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -680,6 +763,16 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -983,12 +1076,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="25" style="23" customWidth="1"/>
     <col min="4" max="4" width="87.1796875" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="8.7265625" customWidth="1"/>
@@ -1007,550 +1100,567 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="18" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="C7" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="16" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="C8" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="E8" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="11" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="B9" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="13" t="s">
+      <c r="C9" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="15" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="17" t="s">
+      <c r="C10" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="E10" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="10" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="C11" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
+      <c r="E11" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="13" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="B12" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="C12" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="17" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="C13" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13" t="s">
+      <c r="E13" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="13" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="15" t="s">
+      <c r="B14" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="C14" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="17" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="C15" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="13" t="s">
+      <c r="E15" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="13" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="15" t="s">
+      <c r="B16" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="C16" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="17" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="C17" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="13" t="s">
+      <c r="E17" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="13" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="15" t="s">
+      <c r="B18" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="C18" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="17" t="s">
+      <c r="E18" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="17" t="s">
+    </row>
+    <row r="19" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="C19" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="13" t="s">
+      <c r="E19" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="13" t="s">
+    </row>
+    <row r="20" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="15" t="s">
+      <c r="B20" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="C20" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="17" t="s">
+    </row>
+    <row r="21" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="C21" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="13" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="13" t="s">
+      <c r="E21" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="13" t="s">
+    </row>
+    <row r="22" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="15" t="s">
+      <c r="B22" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="C22" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="17" t="s">
+      <c r="E22" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="17" t="s">
+    </row>
+    <row r="23" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="C23" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="13" t="s">
+      <c r="E23" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="13" t="s">
+    </row>
+    <row r="24" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="15" t="s">
+      <c r="B24" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="C24" s="22" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="17" t="s">
+      <c r="D24" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="E24" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="C24" s="10" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="C25" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="13" t="s">
+      <c r="E25" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="13" t="s">
+    </row>
+    <row r="26" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="15" t="s">
+      <c r="B26" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="C26" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="17" t="s">
+      <c r="E26" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="17" t="s">
+    </row>
+    <row r="27" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="11" t="s">
+      <c r="B27" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="C27" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" s="13" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="13" t="s">
+      <c r="E27" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B27" s="13" t="s">
+    </row>
+    <row r="28" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="15" t="s">
+      <c r="B28" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="C28" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="17" t="s">
+      <c r="E28" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="17" t="s">
+    </row>
+    <row r="29" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="C29" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="13" t="s">
+      <c r="E29" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="13" t="s">
+    </row>
+    <row r="30" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="15" t="s">
+      <c r="B30" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="C30" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="D30" s="17" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B30" s="17" t="s">
+    </row>
+    <row r="31" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="19" t="s">
+      <c r="B31" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="C31" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13" t="s">
+      <c r="E31" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B31" s="13" t="s">
+    </row>
+    <row r="32" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="15" t="s">
+      <c r="B32" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="C32" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="17" t="s">
+      <c r="E32" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B32" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="C32" s="10" t="s">
+    </row>
+    <row r="33" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B33" s="18">
+        <v>46310</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="18">
+        <v>46311</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B35" s="18">
+        <v>46314</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="D32" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B33" s="20">
-        <v>46310</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="17" t="s">
+      <c r="E35" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="B34" s="20">
-        <v>46311</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="B35" s="20">
-        <v>46314</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35"/>
+    </row>
+    <row r="36" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="18">
+        <v>46316</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D32" r:id="rId1" xr:uid="{9AFE0CE7-2493-40F9-B5D4-B81F15459F22}"/>
@@ -1558,9 +1668,10 @@
     <hyperlink ref="D30" r:id="rId3" xr:uid="{4B33830F-8820-46FB-A14D-8A613E07AF9D}"/>
     <hyperlink ref="D34" r:id="rId4" xr:uid="{388D64DF-7DAC-4F7C-BEDB-BF43D76769C0}"/>
     <hyperlink ref="D35" r:id="rId5" xr:uid="{F9F766B3-B1B2-4252-B68F-AF35E8347C31}"/>
+    <hyperlink ref="D36" r:id="rId6" xr:uid="{3C745628-AF7F-453F-AE45-24047B328936}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -1582,77 +1693,77 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Notes/Class/Kodewala_Batch_Zoom_Recordings_and_Tests.xlsx
+++ b/Notes/Class/Kodewala_Batch_Zoom_Recordings_and_Tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Java-Backend-Development-Journey-\Notes\Class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37625C3-F53D-47E9-ADE6-60364122DB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC6BDB8-FA79-40C4-A031-184B4EA9EF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="187">
   <si>
     <t>Kodewala Academy - 25th Aug Batch 2026</t>
   </si>
@@ -461,9 +461,6 @@
     <t>gzqr=#x7</t>
   </si>
   <si>
-    <t>𝗨𝗻𝗱𝗲𝗿𝘀𝘁𝗮𝗻𝗱𝗶𝗻𝗴 𝗔𝗯𝘀𝘁𝗿𝗮𝗰𝘁𝗶𝗼𝗻</t>
-  </si>
-  <si>
     <t>Deep Dive into Inheritance</t>
   </si>
   <si>
@@ -557,14 +554,41 @@
     <t>7B^U9u$h</t>
   </si>
   <si>
+    <t>Abstraction</t>
+  </si>
+  <si>
+    <t>Method overriding / overloading</t>
+  </si>
+  <si>
+    <t>Day 33</t>
+  </si>
+  <si>
     <t>Polymorphism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://us06web.zoom.us/rec/share/8pPci2NGtYPsEtAOI6lJnaQTVOCmpROBF-Ca7XoPm0_hbag7gL8pGkcLqy9p6m3K.m5uymndxIAKzB8Fz </t>
+  </si>
+  <si>
+    <t>4e8.G.dO</t>
+  </si>
+  <si>
+    <t>Day 34</t>
+  </si>
+  <si>
+    <t>Oops Practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://us06web.zoom.us/rec/share/UBknRFGMJr7DlyCpesHUvezcZPCz-89iquoZd7Eamvz7SN_2xg3kodR32I-C2qgT.Xt2SlASNceq0cYZP </t>
+  </si>
+  <si>
+    <t>#.Yk2.D9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -653,8 +677,34 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF8A1F11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -679,8 +729,14 @@
         <bgColor rgb="FFF2F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -703,12 +759,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -772,7 +873,24 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1076,12 +1194,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="25" style="23" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="87.1796875" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="8.7265625" customWidth="1"/>
@@ -1141,7 +1259,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>14</v>
@@ -1158,7 +1276,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>18</v>
@@ -1175,7 +1293,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>22</v>
@@ -1192,7 +1310,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>26</v>
@@ -1209,7 +1327,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>30</v>
@@ -1226,7 +1344,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>34</v>
@@ -1243,7 +1361,7 @@
         <v>37</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>38</v>
@@ -1260,7 +1378,7 @@
         <v>41</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>42</v>
@@ -1277,7 +1395,7 @@
         <v>45</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>46</v>
@@ -1294,7 +1412,7 @@
         <v>49</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>50</v>
@@ -1311,7 +1429,7 @@
         <v>53</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>54</v>
@@ -1328,7 +1446,7 @@
         <v>57</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>58</v>
@@ -1345,7 +1463,7 @@
         <v>61</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>62</v>
@@ -1362,7 +1480,7 @@
         <v>65</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>66</v>
@@ -1379,7 +1497,7 @@
         <v>69</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>70</v>
@@ -1396,7 +1514,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>74</v>
@@ -1413,7 +1531,7 @@
         <v>77</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>78</v>
@@ -1430,7 +1548,7 @@
         <v>81</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>82</v>
@@ -1464,7 +1582,7 @@
         <v>90</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>91</v>
@@ -1481,7 +1599,7 @@
         <v>94</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>95</v>
@@ -1498,7 +1616,7 @@
         <v>98</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>99</v>
@@ -1515,7 +1633,7 @@
         <v>102</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>103</v>
@@ -1532,7 +1650,7 @@
         <v>106</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>107</v>
@@ -1549,7 +1667,7 @@
         <v>110</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>111</v>
@@ -1566,7 +1684,7 @@
         <v>114</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>115</v>
@@ -1583,7 +1701,7 @@
         <v>118</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D32" s="17" t="s">
         <v>119</v>
@@ -1592,7 +1710,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
         <v>137</v>
       </c>
@@ -1600,7 +1718,7 @@
         <v>46310</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D33" s="17" t="s">
         <v>138</v>
@@ -1609,7 +1727,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
         <v>140</v>
       </c>
@@ -1617,7 +1735,7 @@
         <v>46311</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>141</v>
@@ -1626,7 +1744,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
         <v>143</v>
       </c>
@@ -1634,7 +1752,7 @@
         <v>46314</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>144</v>
@@ -1643,24 +1761,58 @@
         <v>145</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B36" s="18">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>178</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B37" s="18">
+        <v>46317</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="B38" s="24">
+        <v>46318</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="F38" s="28"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D32" r:id="rId1" xr:uid="{9AFE0CE7-2493-40F9-B5D4-B81F15459F22}"/>
@@ -1669,9 +1821,11 @@
     <hyperlink ref="D34" r:id="rId4" xr:uid="{388D64DF-7DAC-4F7C-BEDB-BF43D76769C0}"/>
     <hyperlink ref="D35" r:id="rId5" xr:uid="{F9F766B3-B1B2-4252-B68F-AF35E8347C31}"/>
     <hyperlink ref="D36" r:id="rId6" xr:uid="{3C745628-AF7F-453F-AE45-24047B328936}"/>
+    <hyperlink ref="D37" r:id="rId7" xr:uid="{B8259732-66DC-4D15-B8F0-769448653D6C}"/>
+    <hyperlink ref="D38" r:id="rId8" display="https://us06web.zoom.us/rec/share/UBknRFGMJr7DlyCpesHUvezcZPCz-89iquoZd7Eamvz7SN_2xg3kodR32I-C2qgT.Xt2SlASNceq0cYZP" xr:uid="{B78B14E6-ABAE-41DF-9C32-6AF5BC7B566F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 
